--- a/data/global_stats.xlsx
+++ b/data/global_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\const\DashboardQualityFIVE\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014BB2B1-99EF-499E-A7A7-4C0467EF26F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496E6373-EBCB-420A-BD9B-0CE86912CBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15634" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -486,6 +486,15 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="12.23046875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.07421875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.15234375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.69140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.23046875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.53515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.07421875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.4">

--- a/data/global_stats.xlsx
+++ b/data/global_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\const\DashboardQualityFIVE\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496E6373-EBCB-420A-BD9B-0CE86912CBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EB6974-E18B-4C15-BF14-1F22885FD529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15634" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -546,37 +546,37 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>4</v>
       </c>
       <c r="D2">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1.8333333329999999</v>
       </c>
       <c r="J2">
         <v>16</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">

--- a/data/global_stats.xlsx
+++ b/data/global_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\const\DashboardQualityFIVE\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EB6974-E18B-4C15-BF14-1F22885FD529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C363B82C-1D87-4604-8318-D4D300F74ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15634" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/global_stats.xlsx
+++ b/data/global_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\const\DashboardQualityFIVE\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C363B82C-1D87-4604-8318-D4D300F74ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC2F4A2-4153-499F-98FA-82AB9154AC40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15634" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,20 @@
     <sheet name="global_stats" sheetId="1" r:id="rId1"/>
     <sheet name="README" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -552,10 +565,11 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>0.67</v>
+        <f>(C2+E2/2)/B2</f>
+        <v>0.75</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>12</v>

--- a/data/global_stats.xlsx
+++ b/data/global_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\const\DashboardQualityFIVE\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC2F4A2-4153-499F-98FA-82AB9154AC40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B88CAE-5D10-47DA-93A9-D0EB778D1F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15634" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -188,11 +188,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,16 +577,19 @@
         <v>12</v>
       </c>
       <c r="G2">
+        <f>F2/B2</f>
         <v>2</v>
       </c>
       <c r="H2">
         <v>11</v>
       </c>
-      <c r="I2">
-        <v>1.8333333329999999</v>
-      </c>
-      <c r="J2">
-        <v>16</v>
+      <c r="I2" s="2">
+        <f>H2/B2</f>
+        <v>1.8333333333333333</v>
+      </c>
+      <c r="J2" s="3">
+        <f>1/((F2+H2)/(60*B2))</f>
+        <v>15.65217391304348</v>
       </c>
       <c r="K2">
         <v>3</v>
@@ -598,13 +603,14 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>7</v>
       </c>
       <c r="D3">
-        <v>0.78</v>
+        <f t="shared" ref="D3:D7" si="0">(C3+E3/2)/B3</f>
+        <v>0.7</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -613,22 +619,25 @@
         <v>17</v>
       </c>
       <c r="G3">
-        <v>1.888888889</v>
+        <f t="shared" ref="G3:G5" si="1">F3/B3</f>
+        <v>1.7</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>0.77777777780000001</v>
+        <f t="shared" ref="I3:I5" si="2">H3/B3</f>
+        <v>0.8</v>
       </c>
       <c r="J3">
-        <v>23</v>
+        <f t="shared" ref="J3:J13" si="3">1/((F3+H3)/(60*B3))</f>
+        <v>24</v>
       </c>
       <c r="K3">
         <v>6</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
@@ -641,8 +650,9 @@
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4">
-        <v>0.33</v>
+      <c r="D4" s="2">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -651,16 +661,19 @@
         <v>9</v>
       </c>
       <c r="G4">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="H4">
         <v>2</v>
       </c>
-      <c r="I4">
-        <v>0.66666666669999997</v>
-      </c>
-      <c r="J4">
-        <v>16</v>
+      <c r="I4" s="2">
+        <f t="shared" si="2"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J4" s="3">
+        <f t="shared" si="3"/>
+        <v>16.363636363636363</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -680,6 +693,7 @@
         <v>1</v>
       </c>
       <c r="D5">
+        <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
       <c r="E5">
@@ -689,15 +703,18 @@
         <v>2</v>
       </c>
       <c r="G5">
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="H5">
         <v>4</v>
       </c>
       <c r="I5">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="J5">
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="K5">
@@ -756,6 +773,7 @@
         <v>1</v>
       </c>
       <c r="D7">
+        <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
       <c r="E7">
@@ -765,12 +783,14 @@
         <v>2</v>
       </c>
       <c r="G7">
+        <f>F7/B7</f>
         <v>0.5</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7">
+        <f>H7/B7</f>
         <v>0.25</v>
       </c>
       <c r="J7">
@@ -984,6 +1004,7 @@
         <v>1</v>
       </c>
       <c r="D13">
+        <f t="shared" ref="D13" si="4">(C13+E13/2)/B13</f>
         <v>1</v>
       </c>
       <c r="E13">
@@ -993,12 +1014,14 @@
         <v>3</v>
       </c>
       <c r="G13">
+        <f>F13/B13</f>
         <v>3</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="I13">
+        <f>H13/B13</f>
         <v>1</v>
       </c>
       <c r="J13">

--- a/data/global_stats.xlsx
+++ b/data/global_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\const\DashboardQualityFIVE\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B88CAE-5D10-47DA-93A9-D0EB778D1F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F3F2A6-45FE-4DEF-A77E-2BC03065878C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15634" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -610,17 +610,17 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D7" si="0">(C3+E3/2)/B3</f>
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G5" si="1">F3/B3</f>
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H3">
         <v>8</v>
@@ -630,11 +630,11 @@
         <v>0.8</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J13" si="3">1/((F3+H3)/(60*B3))</f>
-        <v>24</v>
+        <f t="shared" ref="J3:J5" si="3">1/((F3+H3)/(60*B3))</f>
+        <v>23.076923076923077</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L3">
         <v>4</v>

--- a/data/global_stats.xlsx
+++ b/data/global_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\const\DashboardQualityFIVE\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F3F2A6-45FE-4DEF-A77E-2BC03065878C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D07FFF-F80C-4C46-AB74-EA89E8C33FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15634" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -629,7 +629,7 @@
         <f t="shared" ref="I3:I5" si="2">H3/B3</f>
         <v>0.8</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="3">
         <f t="shared" ref="J3:J5" si="3">1/((F3+H3)/(60*B3))</f>
         <v>23.076923076923077</v>
       </c>

--- a/data/global_stats.xlsx
+++ b/data/global_stats.xlsx
@@ -7,11 +7,6 @@
   </sheets>
   <definedNames/>
   <calcPr/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="FfznjTqkPoXkx3QPiqARM1JLBCWu5yqPwak7jLYsTD8="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -406,6 +401,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="6" width="12.63"/>
+    <col customWidth="1" min="10" max="10" width="14.63"/>
     <col customWidth="1" min="12" max="12" width="13.63"/>
   </cols>
   <sheetData>
@@ -458,7 +454,8 @@
         <v>14</v>
       </c>
       <c r="B2" s="4">
-        <v>7.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:B""), ""SELECT COUNT(Col1) WHERE Col1 = '"" &amp; TRIM(A2) &amp; ""' LABEL COUNT(Col1) ''"")"),7.0)</f>
+        <v>7</v>
       </c>
       <c r="C2" s="4">
         <v>5.0</v>
@@ -471,14 +468,16 @@
         <v>1.0</v>
       </c>
       <c r="F2" s="4">
-        <v>14.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:C""), ""SELECT Col2 WHERE Col1 = '"" &amp; A2 &amp; ""'""))"),14.0)</f>
+        <v>14</v>
       </c>
       <c r="G2" s="6">
         <f t="shared" ref="G2:G5" si="2">F2/B2</f>
         <v>2</v>
       </c>
       <c r="H2" s="4">
-        <v>13.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:D""), ""SELECT Col3 WHERE Col1 = '"" &amp; A2 &amp; ""'""))"),13.0)</f>
+        <v>13</v>
       </c>
       <c r="I2" s="7">
         <f t="shared" ref="I2:I5" si="3">H2/B2</f>
@@ -489,10 +488,12 @@
         <v>15.55555556</v>
       </c>
       <c r="K2" s="4">
-        <v>4.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:E""), ""SELECT Col4 WHERE Col1 = '"" &amp; A2 &amp; ""'""))"),4.0)</f>
+        <v>4</v>
       </c>
       <c r="L2" s="4">
-        <v>7.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:F""), ""SELECT Col5 WHERE Col1 = '"" &amp; A2 &amp; ""'""))"),5.0)</f>
+        <v>5</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
@@ -501,42 +502,47 @@
       <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="6">
-        <v>11.0</v>
+      <c r="B3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:B""), ""SELECT COUNT(Col1) WHERE Col1 = '"" &amp; TRIM(A3) &amp; ""' LABEL COUNT(Col1) ''"")"),12.0)</f>
+        <v>12</v>
       </c>
       <c r="C3" s="6">
         <v>7.0</v>
       </c>
       <c r="D3" s="5">
         <f t="shared" si="1"/>
-        <v>0.6818181818</v>
+        <v>0.625</v>
       </c>
       <c r="E3" s="6">
         <v>1.0</v>
       </c>
-      <c r="F3" s="6">
-        <v>20.0</v>
+      <c r="F3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:C""), ""SELECT Col2 WHERE Col1 = '"" &amp; A3 &amp; ""'""))"),21.0)</f>
+        <v>21</v>
       </c>
       <c r="G3" s="6">
         <f t="shared" si="2"/>
-        <v>1.818181818</v>
-      </c>
-      <c r="H3" s="6">
-        <v>9.0</v>
+        <v>1.75</v>
+      </c>
+      <c r="H3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:D""), ""SELECT Col3 WHERE Col1 = '"" &amp; A3 &amp; ""'""))"),12.0)</f>
+        <v>12</v>
       </c>
       <c r="I3" s="7">
         <f t="shared" si="3"/>
-        <v>0.8181818182</v>
+        <v>1</v>
       </c>
       <c r="J3" s="8">
         <f t="shared" si="4"/>
-        <v>22.75862069</v>
-      </c>
-      <c r="K3" s="6">
-        <v>8.0</v>
-      </c>
-      <c r="L3" s="6">
-        <v>5.0</v>
+        <v>21.81818182</v>
+      </c>
+      <c r="K3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:E""), ""SELECT Col4 WHERE Col1 = '"" &amp; A3 &amp; ""'""))"),7.0)</f>
+        <v>7</v>
+      </c>
+      <c r="L3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:F""), ""SELECT Col5 WHERE Col1 = '"" &amp; A3 &amp; ""'""))"),5.0)</f>
+        <v>5</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -545,42 +551,47 @@
       <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="6">
-        <v>3.0</v>
+      <c r="B4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:B""), ""SELECT COUNT(Col1) WHERE Col1 = '"" &amp; TRIM(A4) &amp; ""' LABEL COUNT(Col1) ''"")"),4.0)</f>
+        <v>4</v>
       </c>
       <c r="C4" s="6">
         <v>1.0</v>
       </c>
       <c r="D4" s="5">
         <f t="shared" si="1"/>
-        <v>0.3333333333</v>
+        <v>0.25</v>
       </c>
       <c r="E4" s="6">
         <v>0.0</v>
       </c>
-      <c r="F4" s="6">
-        <v>9.0</v>
+      <c r="F4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:C""), ""SELECT Col2 WHERE Col1 = '"" &amp; A4 &amp; ""'""))"),11.0)</f>
+        <v>11</v>
       </c>
       <c r="G4" s="6">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="H4" s="6">
-        <v>2.0</v>
+        <v>2.75</v>
+      </c>
+      <c r="H4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:D""), ""SELECT Col3 WHERE Col1 = '"" &amp; A4 &amp; ""'""))"),2.0)</f>
+        <v>2</v>
       </c>
       <c r="I4" s="7">
         <f t="shared" si="3"/>
-        <v>0.6666666667</v>
+        <v>0.5</v>
       </c>
       <c r="J4" s="8">
         <f t="shared" si="4"/>
-        <v>16.36363636</v>
-      </c>
-      <c r="K4" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="L4" s="6">
-        <v>2.0</v>
+        <v>18.46153846</v>
+      </c>
+      <c r="K4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:E""), ""SELECT Col4 WHERE Col1 = '"" &amp; A4 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:F""), ""SELECT Col5 WHERE Col1 = '"" &amp; A4 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -589,28 +600,31 @@
       <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="6">
-        <v>4.0</v>
+      <c r="B5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:B""), ""SELECT COUNT(Col1) WHERE Col1 = '"" &amp; TRIM(A5) &amp; ""' LABEL COUNT(Col1) ''"")"),5.0)</f>
+        <v>5</v>
       </c>
       <c r="C5" s="6">
         <v>1.0</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="1"/>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="E5" s="6">
         <v>0.0</v>
       </c>
-      <c r="F5" s="6">
-        <v>2.0</v>
+      <c r="F5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:C""), ""SELECT Col2 WHERE Col1 = '"" &amp; A5 &amp; ""'""))"),3.0)</f>
+        <v>3</v>
       </c>
       <c r="G5" s="6">
         <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-      <c r="H5" s="6">
-        <v>4.0</v>
+        <v>0.6</v>
+      </c>
+      <c r="H5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:D""), ""SELECT Col3 WHERE Col1 = '"" &amp; A5 &amp; ""'""))"),5.0)</f>
+        <v>5</v>
       </c>
       <c r="I5" s="7">
         <f t="shared" si="3"/>
@@ -618,13 +632,15 @@
       </c>
       <c r="J5" s="8">
         <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="K5" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="L5" s="6">
-        <v>3.0</v>
+        <v>37.5</v>
+      </c>
+      <c r="K5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:E""), ""SELECT Col4 WHERE Col1 = '"" &amp; A5 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:F""), ""SELECT Col5 WHERE Col1 = '"" &amp; A5 &amp; ""'""))"),2.0)</f>
+        <v>2</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -633,7 +649,7 @@
       <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="4">
         <v>0.0</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -645,14 +661,16 @@
       <c r="E6" s="6">
         <v>0.0</v>
       </c>
-      <c r="F6" s="6">
-        <v>0.0</v>
+      <c r="F6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:C""), ""SELECT Col2 WHERE Col1 = '"" &amp; A6 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G6" s="6">
         <v>0.0</v>
       </c>
-      <c r="H6" s="6">
-        <v>0.0</v>
+      <c r="H6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:D""), ""SELECT Col3 WHERE Col1 = '"" &amp; A6 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I6" s="7">
         <v>0.0</v>
@@ -660,11 +678,13 @@
       <c r="J6" s="8">
         <v>0.0</v>
       </c>
-      <c r="K6" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="L6" s="6">
-        <v>0.0</v>
+      <c r="K6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:E""), ""SELECT Col4 WHERE Col1 = '"" &amp; A6 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:F""), ""SELECT Col5 WHERE Col1 = '"" &amp; A6 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
@@ -673,28 +693,31 @@
       <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="C7" s="6">
-        <v>2.0</v>
+      <c r="B7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:B""), ""SELECT COUNT(Col1) WHERE Col1 = '"" &amp; TRIM(A7) &amp; ""' LABEL COUNT(Col1) ''"")"),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="C7" s="4">
+        <v>3.0</v>
       </c>
       <c r="D7" s="5">
         <f>(C7+E7/2)/B7</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E7" s="6">
         <v>0.0</v>
       </c>
-      <c r="F7" s="6">
-        <v>4.0</v>
+      <c r="F7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:C""), ""SELECT Col2 WHERE Col1 = '"" &amp; A7 &amp; ""'""))"),7.0)</f>
+        <v>7</v>
       </c>
       <c r="G7" s="6">
         <f>F7/B7</f>
-        <v>0.8</v>
-      </c>
-      <c r="H7" s="6">
-        <v>1.0</v>
+        <v>1.4</v>
+      </c>
+      <c r="H7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:D""), ""SELECT Col3 WHERE Col1 = '"" &amp; A7 &amp; ""'""))"),1.0)</f>
+        <v>1</v>
       </c>
       <c r="I7" s="7">
         <f>H7/B7</f>
@@ -702,13 +725,15 @@
       </c>
       <c r="J7" s="8">
         <f>1/((F7+H7)/(60*B7))</f>
-        <v>60</v>
-      </c>
-      <c r="K7" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="L7" s="6">
-        <v>0.0</v>
+        <v>37.5</v>
+      </c>
+      <c r="K7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:E""), ""SELECT Col4 WHERE Col1 = '"" &amp; A7 &amp; ""'""))"),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="L7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:F""), ""SELECT Col5 WHERE Col1 = '"" &amp; A7 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -717,7 +742,7 @@
       <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="4">
         <v>0.0</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -729,14 +754,16 @@
       <c r="E8" s="6">
         <v>0.0</v>
       </c>
-      <c r="F8" s="6">
-        <v>0.0</v>
+      <c r="F8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:C""), ""SELECT Col2 WHERE Col1 = '"" &amp; A8 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G8" s="6">
         <v>0.0</v>
       </c>
-      <c r="H8" s="6">
-        <v>0.0</v>
+      <c r="H8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:D""), ""SELECT Col3 WHERE Col1 = '"" &amp; A8 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I8" s="7">
         <v>0.0</v>
@@ -744,11 +771,13 @@
       <c r="J8" s="8">
         <v>0.0</v>
       </c>
-      <c r="K8" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="L8" s="6">
-        <v>0.0</v>
+      <c r="K8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:E""), ""SELECT Col4 WHERE Col1 = '"" &amp; A8 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:F""), ""SELECT Col5 WHERE Col1 = '"" &amp; A8 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
@@ -757,7 +786,7 @@
       <c r="A9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="4">
         <v>0.0</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -769,14 +798,16 @@
       <c r="E9" s="6">
         <v>0.0</v>
       </c>
-      <c r="F9" s="6">
-        <v>0.0</v>
+      <c r="F9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:C""), ""SELECT Col2 WHERE Col1 = '"" &amp; A9 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G9" s="6">
         <v>0.0</v>
       </c>
-      <c r="H9" s="6">
-        <v>0.0</v>
+      <c r="H9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:D""), ""SELECT Col3 WHERE Col1 = '"" &amp; A9 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I9" s="7">
         <v>0.0</v>
@@ -784,11 +815,13 @@
       <c r="J9" s="8">
         <v>0.0</v>
       </c>
-      <c r="K9" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="L9" s="6">
-        <v>0.0</v>
+      <c r="K9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:E""), ""SELECT Col4 WHERE Col1 = '"" &amp; A9 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:F""), ""SELECT Col5 WHERE Col1 = '"" &amp; A9 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
@@ -797,7 +830,7 @@
       <c r="A10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="4">
         <v>0.0</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -809,14 +842,16 @@
       <c r="E10" s="6">
         <v>0.0</v>
       </c>
-      <c r="F10" s="6">
-        <v>0.0</v>
+      <c r="F10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:C""), ""SELECT Col2 WHERE Col1 = '"" &amp; A10 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G10" s="6">
         <v>0.0</v>
       </c>
-      <c r="H10" s="6">
-        <v>0.0</v>
+      <c r="H10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:D""), ""SELECT Col3 WHERE Col1 = '"" &amp; A10 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I10" s="7">
         <v>0.0</v>
@@ -824,11 +859,13 @@
       <c r="J10" s="8">
         <v>0.0</v>
       </c>
-      <c r="K10" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="L10" s="6">
-        <v>0.0</v>
+      <c r="K10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:E""), ""SELECT Col4 WHERE Col1 = '"" &amp; A10 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:F""), ""SELECT Col5 WHERE Col1 = '"" &amp; A10 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
@@ -837,7 +874,7 @@
       <c r="A11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="4">
         <v>0.0</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -849,14 +886,16 @@
       <c r="E11" s="6">
         <v>0.0</v>
       </c>
-      <c r="F11" s="6">
-        <v>0.0</v>
+      <c r="F11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:C""), ""SELECT Col2 WHERE Col1 = '"" &amp; A11 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G11" s="6">
         <v>0.0</v>
       </c>
-      <c r="H11" s="6">
-        <v>0.0</v>
+      <c r="H11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:D""), ""SELECT Col3 WHERE Col1 = '"" &amp; A11 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I11" s="7">
         <v>0.0</v>
@@ -864,11 +903,13 @@
       <c r="J11" s="8">
         <v>0.0</v>
       </c>
-      <c r="K11" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="L11" s="6">
-        <v>0.0</v>
+      <c r="K11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:E""), ""SELECT Col4 WHERE Col1 = '"" &amp; A11 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:F""), ""SELECT Col5 WHERE Col1 = '"" &amp; A11 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
@@ -877,7 +918,7 @@
       <c r="A12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="4">
         <v>0.0</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -889,14 +930,16 @@
       <c r="E12" s="6">
         <v>0.0</v>
       </c>
-      <c r="F12" s="6">
-        <v>0.0</v>
+      <c r="F12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:C""), ""SELECT Col2 WHERE Col1 = '"" &amp; A12 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="G12" s="6">
         <v>0.0</v>
       </c>
-      <c r="H12" s="6">
-        <v>0.0</v>
+      <c r="H12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:D""), ""SELECT Col3 WHERE Col1 = '"" &amp; A12 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I12" s="7">
         <v>0.0</v>
@@ -904,11 +947,13 @@
       <c r="J12" s="8">
         <v>0.0</v>
       </c>
-      <c r="K12" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="L12" s="6">
-        <v>0.0</v>
+      <c r="K12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:E""), ""SELECT Col4 WHERE Col1 = '"" &amp; A12 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:F""), ""SELECT Col5 WHERE Col1 = '"" &amp; A12 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
@@ -917,8 +962,9 @@
       <c r="A13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="6">
-        <v>1.0</v>
+      <c r="B13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:B""), ""SELECT COUNT(Col1) WHERE Col1 = '"" &amp; TRIM(A13) &amp; ""' LABEL COUNT(Col1) ''"")"),1.0)</f>
+        <v>1</v>
       </c>
       <c r="C13" s="6">
         <v>1.0</v>
@@ -930,15 +976,17 @@
       <c r="E13" s="6">
         <v>0.0</v>
       </c>
-      <c r="F13" s="6">
-        <v>3.0</v>
+      <c r="F13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:C""), ""SELECT Col2 WHERE Col1 = '"" &amp; A13 &amp; ""'""))"),3.0)</f>
+        <v>3</v>
       </c>
       <c r="G13" s="6">
         <f>F13/B13</f>
         <v>3</v>
       </c>
-      <c r="H13" s="6">
-        <v>1.0</v>
+      <c r="H13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:D""), ""SELECT Col3 WHERE Col1 = '"" &amp; A13 &amp; ""'""))"),1.0)</f>
+        <v>1</v>
       </c>
       <c r="I13" s="7">
         <f>H13/B13</f>
@@ -948,11 +996,13 @@
         <f>1/((F13+H13)/(60*B13))</f>
         <v>15</v>
       </c>
-      <c r="K13" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="L13" s="6">
-        <v>1.0</v>
+      <c r="K13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:E""), ""SELECT Col4 WHERE Col1 = '"" &amp; A13 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:F""), ""SELECT Col5 WHERE Col1 = '"" &amp; A13 &amp; ""'""))"),0.0)</f>
+        <v>0</v>
       </c>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>

--- a/data/global_stats.xlsx
+++ b/data/global_stats.xlsx
@@ -454,15 +454,15 @@
         <v>14</v>
       </c>
       <c r="B2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:B""), ""SELECT COUNT(Col1) WHERE Col1 = '"" &amp; TRIM(A2) &amp; ""' LABEL COUNT(Col1) ''"")"),7.0)</f>
-        <v>7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:B""), ""SELECT COUNT(Col1) WHERE Col1 = '"" &amp; TRIM(A2) &amp; ""' LABEL COUNT(Col1) ''"")"),8.0)</f>
+        <v>8</v>
       </c>
       <c r="C2" s="4">
         <v>5.0</v>
       </c>
       <c r="D2" s="5">
         <f t="shared" ref="D2:D5" si="1">(C2+E2/2)/B2</f>
-        <v>0.7857142857</v>
+        <v>0.6875</v>
       </c>
       <c r="E2" s="6">
         <v>1.0</v>
@@ -473,27 +473,27 @@
       </c>
       <c r="G2" s="6">
         <f t="shared" ref="G2:G5" si="2">F2/B2</f>
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="H2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:D""), ""SELECT Col3 WHERE Col1 = '"" &amp; A2 &amp; ""'""))"),13.0)</f>
-        <v>13</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:D""), ""SELECT Col3 WHERE Col1 = '"" &amp; A2 &amp; ""'""))"),15.0)</f>
+        <v>15</v>
       </c>
       <c r="I2" s="7">
         <f t="shared" ref="I2:I5" si="3">H2/B2</f>
-        <v>1.857142857</v>
+        <v>1.875</v>
       </c>
       <c r="J2" s="8">
         <f t="shared" ref="J2:J5" si="4">1/((F2+H2)/(60*B2))</f>
-        <v>15.55555556</v>
+        <v>16.55172414</v>
       </c>
       <c r="K2" s="4">
         <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:E""), ""SELECT Col4 WHERE Col1 = '"" &amp; A2 &amp; ""'""))"),4.0)</f>
         <v>4</v>
       </c>
       <c r="L2" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:F""), ""SELECT Col5 WHERE Col1 = '"" &amp; A2 &amp; ""'""))"),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:F""), ""SELECT Col5 WHERE Col1 = '"" &amp; A2 &amp; ""'""))"),6.0)</f>
+        <v>6</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
@@ -601,46 +601,46 @@
         <v>17</v>
       </c>
       <c r="B5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:B""), ""SELECT COUNT(Col1) WHERE Col1 = '"" &amp; TRIM(A5) &amp; ""' LABEL COUNT(Col1) ''"")"),5.0)</f>
-        <v>5</v>
-      </c>
-      <c r="C5" s="6">
-        <v>1.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:B""), ""SELECT COUNT(Col1) WHERE Col1 = '"" &amp; TRIM(A5) &amp; ""' LABEL COUNT(Col1) ''"")"),6.0)</f>
+        <v>6</v>
+      </c>
+      <c r="C5" s="4">
+        <v>2.0</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0.3333333333</v>
       </c>
       <c r="E5" s="6">
         <v>0.0</v>
       </c>
       <c r="F5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:C""), ""SELECT Col2 WHERE Col1 = '"" &amp; A5 &amp; ""'""))"),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:C""), ""SELECT Col2 WHERE Col1 = '"" &amp; A5 &amp; ""'""))"),4.0)</f>
+        <v>4</v>
       </c>
       <c r="G5" s="6">
         <f t="shared" si="2"/>
-        <v>0.6</v>
+        <v>0.6666666667</v>
       </c>
       <c r="H5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:D""), ""SELECT Col3 WHERE Col1 = '"" &amp; A5 &amp; ""'""))"),5.0)</f>
-        <v>5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:D""), ""SELECT Col3 WHERE Col1 = '"" &amp; A5 &amp; ""'""))"),7.0)</f>
+        <v>7</v>
       </c>
       <c r="I5" s="7">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>1.166666667</v>
       </c>
       <c r="J5" s="8">
         <f t="shared" si="4"/>
-        <v>37.5</v>
+        <v>32.72727273</v>
       </c>
       <c r="K5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:E""), ""SELECT Col4 WHERE Col1 = '"" &amp; A5 &amp; ""'""))"),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:E""), ""SELECT Col4 WHERE Col1 = '"" &amp; A5 &amp; ""'""))"),1.0)</f>
+        <v>1</v>
       </c>
       <c r="L5" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:F""), ""SELECT Col5 WHERE Col1 = '"" &amp; A5 &amp; ""'""))"),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SUM(QUERY(IMPORTRANGE(""1VF259H18U7gWcFqLPk9T1ETvtyPzZJvqcyJZchpB9MY"", ""Feuil1!B:F""), ""SELECT Col5 WHERE Col1 = '"" &amp; A5 &amp; ""'""))"),3.0)</f>
+        <v>3</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
